--- a/samples/month-close/month-close.xlsx
+++ b/samples/month-close/month-close.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Where the money is'!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bridge by channel'!$A$1:$D$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exceptions'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Exceptions'!$A$1:$H$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Bank credits'!$A$1:$E$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Payments out'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Files'!$A$1:$B$12</definedName>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-17266.45</v>
+        <v>-17274.48</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>-1210.83</v>
@@ -499,11 +499,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Paid out, arriving in April</t>
+          <t>Paid out in March, booked in April</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-68200.14999999999</v>
+        <v>-42234.27</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>0</v>
@@ -512,11 +512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Not yet paid out</t>
+          <t>Not yet paid out on 31 March</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-7690.05</v>
+        <v>-33655.93</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>0</v>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-904.0700000000001</v>
+        <v>-369.12</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>0</v>
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>421581.88</v>
+        <v>422108.8</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>32753.08</v>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>129.75</v>
+        <v>664.7</v>
       </c>
     </row>
     <row r="4">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>-4624.84</v>
+        <v>-4632.87</v>
       </c>
     </row>
     <row r="8">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>-44761.31</v>
+        <v>-28818.18</v>
       </c>
     </row>
     <row r="9">
@@ -791,7 +791,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Not yet paid out</t>
+          <t>Not yet paid out on 31 March</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0</v>
+        <v>-15943.13</v>
       </c>
     </row>
     <row r="10">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>190261.8</v>
+        <v>190788.72</v>
       </c>
     </row>
     <row r="12">
@@ -1595,7 +1595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1700,37 +1700,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Order paid, no card charge</t>
+          <t>Charged less than the order</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>#8935</t>
+          <t>#9838</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>337.85</t>
+          <t>273.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>260.50</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-337.85</t>
+          <t>-12.50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Ask Shopify support; the order may have been marked paid by hand</t>
+          <t>Collect the difference or correct the order</t>
         </is>
       </c>
     </row>
@@ -1742,22 +1742,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charged less than the order</t>
+          <t>Order paid, no card charge</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>#8345</t>
+          <t>#8935</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.95</t>
+          <t>337.85</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>48.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-337.85</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Collect the difference or correct the order</t>
+          <t>Ask Shopify support; the order may have been marked paid by hand</t>
         </is>
       </c>
     </row>
@@ -1789,17 +1789,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>#7596</t>
+          <t>#8345</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>52.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>48.00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.50</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1868,37 +1868,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charge with no order</t>
+          <t>Card charged for an order paid through PayPal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>#10662</t>
+          <t>#9031</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>47.95</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>129.00</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>129.00</t>
+          <t>47.95</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Find the order; the export may predate it</t>
+          <t>The customer paid twice: refund one of the two payments</t>
         </is>
       </c>
     </row>
@@ -1910,37 +1910,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charge with no order</t>
+          <t>Card charged for an order paid through PayPal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>#10666</t>
+          <t>#9490</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>745.00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>745.00</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>129.00</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>129.00</t>
+          <t>745.00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Find the order; the export may predate it</t>
+          <t>The customer paid twice: refund one of the two payments</t>
         </is>
       </c>
     </row>
@@ -1952,106 +1952,106 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Payout never reached the bank</t>
+          <t>Card refund differs from the order's refund</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>payout 2026-03-18</t>
+          <t>#9090</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>103.95</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>9341.59</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9341.59</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Ask Shopify for the payout's trace; check the bank account on file</t>
+          <t>Find who refunded the difference and why</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Shopify Payments</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Order paid, no PayPal payment</t>
+          <t>Adjustment with no order</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>#8041</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>582.00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>-23.40</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-582.00</t>
+          <t>-23.40</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Search PayPal by the customer's e-mail; the order may be marked paid by mistake</t>
+          <t>Ask Shopify what the adjustment was for</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Shopify Payments</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Refund in PayPal, none in the shop</t>
+          <t>Chargeback, the order still reads paid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>#9232</t>
+          <t>#7795</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>154.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-45.00</t>
+          <t>-154.00 and a 15.00 fee</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2061,39 +2061,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-45.00</t>
+          <t>-169.00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Find who refunded it and why; record it in the shop or claim it back</t>
+          <t>Answer the dispute, or record it on the order</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Shopify Payments</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fee above the contract (3.49% for 2.99%)</t>
+          <t>Payout never reached the bank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KL202603234928</t>
+          <t>payout 2026-03-18</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.99%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>9341.59</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2103,41 +2103,41 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-146.50</t>
+          <t>-9341.59</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Claim the difference from Klarna</t>
+          <t>Ask Shopify for the payout's trace; check the bank account on file</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Held back as a rolling reserve</t>
+          <t>Order paid, no PayPal payment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KL202603234928</t>
+          <t>#8041</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>582.00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2000.00</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>—</t>
@@ -2145,123 +2145,123 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2000.00</t>
+          <t>-582.00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ask Klarna why and until when; it is the shop's money</t>
+          <t>Search PayPal by the customer's e-mail; the order may be marked paid by mistake</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bank transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Customer paid a different amount</t>
+          <t>Refund in PayPal, none in the shop</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>#8067</t>
+          <t>#9232</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>224.10</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>-45.00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>209.10</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-15.00</t>
+          <t>-45.00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Probably the customer's bank charges; invoice them or write it off</t>
+          <t>Find who refunded it and why; record it in the shop or claim it back</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deposit differs from the till</t>
+          <t>Fee above the contract (3.49% for 2.99%)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>week of 09 March</t>
+          <t>KL202603234928</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1748.00</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>3.49%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1708.00</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-40.00</t>
+          <t>-146.50</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Count the till against the day reports of that week</t>
+          <t>Claim the difference from Klarna</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cancelled, but charged</t>
+          <t>Held back as a rolling reserve</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>302-2534212-3499741 NO-BTL-75</t>
+          <t>KL202603234928</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cancelled</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2271,96 +2271,96 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>27.90</t>
+          <t>-2000.00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Refund the customer</t>
+          <t>Ask Klarna why and until when; it is the shop's money</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Bank transfer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Paid less than the price</t>
+          <t>Customer paid a different amount</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>304-4103772-7671362 NO-CBL-02</t>
+          <t>#8067</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>14.90</t>
+          <t>224.10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209.10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.00</t>
+          <t>-15.00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Open a case with Seller Support</t>
+          <t>Probably the customer's bank charges; invoice them or write it off</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Commission above the rate card</t>
+          <t>Deposit differs from the till</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>302-5103311-7220635 NO-PWR-10</t>
+          <t>week of 09 March</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1748.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1708.00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-40.00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Open a case with Seller Support</t>
+          <t>Count the till against the day reports of that week</t>
         </is>
       </c>
     </row>
@@ -2372,37 +2372,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shipped, never paid</t>
+          <t>Cancelled, but charged</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>306-2995046-5638590 NO-SCK-02</t>
+          <t>302-2534212-3499741 NO-BTL-75</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>24.90</t>
+          <t>Cancelled</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>27.90</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-24.90</t>
+          <t>27.90</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Open a case with Seller Support</t>
+          <t>Refund the customer</t>
         </is>
       </c>
     </row>
@@ -2414,22 +2414,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FBA fee charged twice</t>
+          <t>Paid less than the price</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>303-3618526-6250112 NO-SCK-02</t>
+          <t>304-4103772-7671362 NO-CBL-02</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>14.90</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-5.00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shipped, never paid</t>
+          <t>Commission above the rate card</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>304-7670079-7856065 NO-LMP-35</t>
+          <t>302-5103311-7220635 NO-PWR-10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>39.90</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-39.90</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>304-7670079-7856065 NO-SPK-01</t>
+          <t>306-2995046-5638590 NO-SCK-02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>39.80</t>
+          <t>24.90</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-39.80</t>
+          <t>-24.90</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2540,37 +2540,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Charge with no order in the report</t>
+          <t>FBA fee charged twice</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>302-8819284-1290456 NO-LMP-35</t>
+          <t>303-3618526-6250112 NO-SCK-02</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>39.90</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>39.90</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Check whether the report was pulled before this order</t>
+          <t>Open a case with Seller Support</t>
         </is>
       </c>
     </row>
@@ -2582,22 +2582,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Refund larger than the sale</t>
+          <t>Shipped, never paid</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>304-4179934-8659362 NO-GLV-01</t>
+          <t>304-7670079-7856065 NO-LMP-35</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>34.90</t>
+          <t>39.90</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>69.80</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-34.90</t>
+          <t>-39.90</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2619,22 +2619,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stripe (USD)</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Invoice due, not paid</t>
+          <t>Shipped, never paid</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NO-US-2026-007</t>
+          <t>304-7670079-7856065 NO-SPK-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>USD 3880.00</t>
+          <t>39.80</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2649,59 +2649,185 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>USD -3880.00</t>
+          <t>-39.80</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Remind the customer</t>
+          <t>Open a case with Seller Support</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Charge with no order in the report</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>302-8819284-1290456 NO-LMP-35</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>39.90</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>39.90</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Check whether the report was pulled before this order</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Refund larger than the sale</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>304-4179934-8659362 NO-GLV-01</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>34.90</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>69.80</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-34.90</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Open a case with Seller Support</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Stripe (USD)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Invoice due, not paid</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NO-US-2026-007</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>USD 3880.00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>USD -3880.00</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Remind the customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Bank</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Credit nobody can place</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>26.03.2026</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>310.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>310.00</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Ask the bank for the payer's details</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H26"/>
+  <autoFilter ref="A1:H29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3216,7 +3342,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5379.39</v>
+        <v>5391.71</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -5191,7 +5317,7 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>7510.83</v>
+        <v>7557.81</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -5516,7 +5642,7 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>25246.56</v>
+        <v>25980.14</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -6162,7 +6288,7 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>10324.94</v>
+        <v>10198.12</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -6237,7 +6363,7 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>5824.55</v>
+        <v>5685.41</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -6399,7 +6525,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>36d1113a3df13b412067c5662c80a93f72ffd7ae80c284ead5ed230909023e3f</t>
+          <t>d8b8a2459bdb1c07c4f3202c3279920270ae6d9715accf44b9a405b4e63d91c1</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6621,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>f34ebeec83a7afbd9095a65dde36e2cdde8348766e9791df0ef97e4c8d037803</t>
+          <t>0b157efe69ed3899acdd27ab9f19af9a0ad2ec331a485bf855700523f8b3b234</t>
         </is>
       </c>
     </row>
